--- a/data/trans_bre/P6904-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P6904-Provincia-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-36,55; 12,58</t>
+          <t>-36,03; 12,83</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-17,92; 32,29</t>
+          <t>-18,59; 31,47</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9,53; 48,22</t>
+          <t>8,83; 48,17</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,67; 50,52</t>
+          <t>-4,98; 50,55</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-49,4; 21,6</t>
+          <t>-50,32; 21,16</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-26,07; 70,68</t>
+          <t>-27,83; 65,61</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>19,55; 170,52</t>
+          <t>17,45; 168,75</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-4,43; 134,21</t>
+          <t>-5,26; 128,62</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-11,2; 31,29</t>
+          <t>-12,29; 27,99</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-48,13; -2,6</t>
+          <t>-46,4; -3,87</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-13,08; 19,12</t>
+          <t>-12,8; 20,43</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-29,13; 17,69</t>
+          <t>-26,77; 19,17</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-19,09; 74,47</t>
+          <t>-21,89; 66,13</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-66,66; -4,08</t>
+          <t>-65,92; -5,81</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-16,51; 28,45</t>
+          <t>-16,28; 30,46</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-41,89; 41,27</t>
+          <t>-38,29; 49,25</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-40,0; 11,45</t>
+          <t>-39,55; 11,74</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-46,39; 14,92</t>
+          <t>-45,25; 13,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-50,07; 7,58</t>
+          <t>-48,88; 10,27</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-11,78; 23,83</t>
+          <t>-14,8; 23,88</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-65,02; 24,95</t>
+          <t>-63,99; 28,45</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-66,64; 29,07</t>
+          <t>-63,56; 27,55</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-56,77; 9,69</t>
+          <t>-57,05; 13,21</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-19,58; 62,65</t>
+          <t>-22,82; 58,84</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-23,74; 23,9</t>
+          <t>-25,34; 23,85</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-23,01; 25,56</t>
+          <t>-22,75; 26,51</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-28,05; 20,87</t>
+          <t>-28,14; 19,41</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-7,1; 36,86</t>
+          <t>-6,62; 37,63</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-49,9; 71,04</t>
+          <t>-51,08; 75,33</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-39,02; 69,36</t>
+          <t>-36,24; 71,56</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-35,51; 39,13</t>
+          <t>-35,88; 35,73</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-8,67; 64,79</t>
+          <t>-8,22; 68,2</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-50,09; 22,47</t>
+          <t>-51,59; 16,45</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-58,25; 10,68</t>
+          <t>-57,54; 11,19</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-24,08; 60,81</t>
+          <t>-24,28; 59,44</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-28,64; 25,2</t>
+          <t>-28,64; 27,75</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 126,97</t>
+          <t>-100,0; 83,47</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-64,41; 12,52</t>
+          <t>-62,51; 14,29</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-26,05; 185,78</t>
+          <t>-27,73; 176,59</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-48,83; 77,89</t>
+          <t>-46,91; 91,08</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-27,87; 30,64</t>
+          <t>-27,63; 33,18</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-53,73; -0,5</t>
+          <t>-55,34; -1,19</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>10,32; 75,23</t>
+          <t>10,71; 77,39</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-24,81; 17,28</t>
+          <t>-26,33; 16,1</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-62,26; 97,66</t>
+          <t>-60,05; 111,48</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-88,72; -0,14</t>
+          <t>-88,61; 0,58</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>32,37; 414,08</t>
+          <t>32,48; 392,41</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-34,29; 34,5</t>
+          <t>-37,15; 34,08</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-15,6; 21,16</t>
+          <t>-15,65; 22,68</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-3,97; 35,24</t>
+          <t>-4,79; 35,22</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-25,45; 10,19</t>
+          <t>-24,42; 10,57</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-7,09; 25,44</t>
+          <t>-6,48; 23,82</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-29,29; 48,23</t>
+          <t>-27,8; 57,14</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-8,36; 120,44</t>
+          <t>-9,27; 116,27</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-34,54; 18,06</t>
+          <t>-33,65; 19,02</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-10,58; 54,23</t>
+          <t>-9,81; 50,59</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-17,02; 17,12</t>
+          <t>-16,57; 15,17</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-9,12; 37,64</t>
+          <t>-10,61; 37,39</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-10,68; 40,68</t>
+          <t>-12,06; 41,01</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-39,67; -2,21</t>
+          <t>-39,47; -3,25</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-24,82; 30,29</t>
+          <t>-24,71; 27,34</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-18,72; 123,9</t>
+          <t>-20,76; 123,04</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-24,31; 149,75</t>
+          <t>-22,99; 175,89</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-48,66; -3,31</t>
+          <t>-48,87; -4,66</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-9,04; 7,74</t>
+          <t>-8,75; 8,36</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-12,72; 5,03</t>
+          <t>-11,66; 5,43</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,16; 16,18</t>
+          <t>-0,49; 16,47</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-4,06; 15,77</t>
+          <t>-4,16; 16,37</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-16,13; 15,39</t>
+          <t>-15,95; 17,22</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-22,0; 9,79</t>
+          <t>-20,07; 10,93</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-0,31; 29,22</t>
+          <t>-0,73; 29,48</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-6,5; 27,33</t>
+          <t>-6,62; 29,39</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P6904-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P6904-Provincia-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>25,4</t>
+          <t>13,12</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>44,01%</t>
+          <t>19,68%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-36,03; 12,83</t>
+          <t>-39,64; 11,29</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-18,59; 31,47</t>
+          <t>-18,52; 31,56</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8,83; 48,17</t>
+          <t>7,97; 47,63</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-4,98; 50,55</t>
+          <t>-14,37; 36,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-50,32; 21,16</t>
+          <t>-54,61; 20,65</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-27,83; 65,61</t>
+          <t>-26,94; 67,8</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>17,45; 168,75</t>
+          <t>14,96; 163,19</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-5,26; 128,62</t>
+          <t>-14,89; 76,47</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-4,62</t>
+          <t>-5,69</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-8,11%</t>
+          <t>-9,61%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-12,29; 27,99</t>
+          <t>-15,36; 28,63</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-46,4; -3,87</t>
+          <t>-46,77; -4,24</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-12,8; 20,43</t>
+          <t>-12,9; 20,04</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-26,77; 19,17</t>
+          <t>-26,11; 14,7</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-21,89; 66,13</t>
+          <t>-26,11; 66,78</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-65,92; -5,81</t>
+          <t>-66,72; -7,44</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-16,28; 30,46</t>
+          <t>-16,22; 28,93</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-38,29; 49,25</t>
+          <t>-37,08; 32,08</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4,69</t>
+          <t>3,51</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>6,75%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-39,55; 11,74</t>
+          <t>-39,22; 13,85</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-45,25; 13,0</t>
+          <t>-46,85; 15,48</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-48,88; 10,27</t>
+          <t>-48,93; 12,61</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-14,8; 23,88</t>
+          <t>-15,64; 20,39</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-63,99; 28,45</t>
+          <t>-61,08; 33,15</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-63,56; 27,55</t>
+          <t>-65,59; 32,31</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-57,05; 13,21</t>
+          <t>-57,84; 16,45</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-22,82; 58,84</t>
+          <t>-24,86; 48,38</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11,03</t>
+          <t>6,19</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>8,38%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-25,34; 23,85</t>
+          <t>-23,58; 26,01</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-22,75; 26,51</t>
+          <t>-21,81; 25,96</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-28,14; 19,41</t>
+          <t>-29,98; 20,08</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-6,62; 37,63</t>
+          <t>-10,12; 28,11</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-51,08; 75,33</t>
+          <t>-51,93; 84,96</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-36,24; 71,56</t>
+          <t>-37,84; 62,35</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-35,88; 35,73</t>
+          <t>-37,97; 36,45</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-8,22; 68,2</t>
+          <t>-12,26; 49,25</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-1,7</t>
+          <t>-2,92</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-3,64%</t>
+          <t>-6,05%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-51,59; 16,45</t>
+          <t>-51,88; 22,78</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-57,54; 11,19</t>
+          <t>-57,53; 12,41</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-24,28; 59,44</t>
+          <t>-17,51; 59,1</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-28,64; 27,75</t>
+          <t>-28,55; 25,06</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 83,47</t>
+          <t>-100,0; 127,76</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-62,51; 14,29</t>
+          <t>-62,51; 13,06</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-27,73; 176,59</t>
+          <t>-22,68; 194,47</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-46,91; 91,08</t>
+          <t>-48,08; 73,12</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-4,52</t>
+          <t>-6,64</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>-7,31%</t>
+          <t>-10,33%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-27,63; 33,18</t>
+          <t>-29,2; 34,43</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-55,34; -1,19</t>
+          <t>-55,15; -3,83</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>10,71; 77,39</t>
+          <t>15,04; 78,12</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-26,33; 16,1</t>
+          <t>-27,44; 12,45</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-60,05; 111,48</t>
+          <t>-60,44; 102,7</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-88,61; 0,58</t>
+          <t>-88,83; -4,14</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>32,48; 392,41</t>
+          <t>34,82; 447,68</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-37,15; 34,08</t>
+          <t>-37,12; 23,44</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>9,41</t>
+          <t>6,63</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>16,61%</t>
+          <t>11,36%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-15,65; 22,68</t>
+          <t>-15,54; 20,41</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-4,79; 35,22</t>
+          <t>-4,21; 38,63</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-24,42; 10,57</t>
+          <t>-25,92; 9,9</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-6,48; 23,82</t>
+          <t>-9,77; 22,19</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-27,8; 57,14</t>
+          <t>-28,51; 49,12</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-9,27; 116,27</t>
+          <t>-8,72; 131,52</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-33,65; 19,02</t>
+          <t>-36,85; 16,45</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-9,81; 50,59</t>
+          <t>-14,51; 44,73</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>-22,24</t>
+          <t>-27,08</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>-29,37%</t>
+          <t>-35,96%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-16,57; 15,17</t>
+          <t>-15,75; 16,94</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-10,61; 37,39</t>
+          <t>-8,9; 37,41</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-12,06; 41,01</t>
+          <t>-9,13; 42,15</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-39,47; -3,25</t>
+          <t>-42,52; -9,4</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-24,71; 27,34</t>
+          <t>-23,46; 29,59</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-20,76; 123,04</t>
+          <t>-17,72; 118,28</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-22,99; 175,89</t>
+          <t>-21,27; 186,7</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-48,87; -4,66</t>
+          <t>-53,24; -14,98</t>
         </is>
       </c>
     </row>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>3,79</t>
+          <t>-2,31</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>-3,65%</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-8,75; 8,36</t>
+          <t>-8,72; 7,71</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-11,66; 5,43</t>
+          <t>-12,06; 5,98</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,49; 16,47</t>
+          <t>-1,05; 15,55</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-4,16; 16,37</t>
+          <t>-9,12; 4,34</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-15,95; 17,22</t>
+          <t>-15,42; 15,7</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-20,07; 10,93</t>
+          <t>-20,8; 11,88</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-0,73; 29,48</t>
+          <t>-1,7; 28,47</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-6,62; 29,39</t>
+          <t>-13,64; 7,32</t>
         </is>
       </c>
     </row>
